--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20231.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,40 +73,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
   </si>
 </sst>
 </file>
@@ -598,16 +571,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -621,16 +597,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -686,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -712,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -731,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -763,93 +742,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920286</v>
+        <v>22330051920153</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920155</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920367</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920175</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20231.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,15 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
   </si>
 </sst>
 </file>
@@ -665,16 +656,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -740,29 +731,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920153</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20231.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20231.xlsx
@@ -665,7 +665,7 @@
         <v>94.44</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,7 +691,7 @@
         <v>92</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20231.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20231.xlsx
@@ -665,7 +665,7 @@
         <v>94.44</v>
       </c>
       <c r="H2">
-        <v>9.699999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,7 +691,7 @@
         <v>92</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
